--- a/results-excel/turnover_tax_analysis.xlsx
+++ b/results-excel/turnover_tax_analysis.xlsx
@@ -448,7 +448,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B2" t="n">
         <v>10</v>
@@ -460,12 +460,12 @@
         <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>31.31</v>
+        <v>30.91</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B3" t="n">
         <v>9</v>
@@ -477,12 +477,12 @@
         <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>26.76</v>
+        <v>25.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B4" t="n">
         <v>9</v>
@@ -494,12 +494,12 @@
         <v>51</v>
       </c>
       <c r="E4" t="n">
-        <v>26.54</v>
+        <v>25.81</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B5" t="n">
         <v>7</v>
@@ -511,12 +511,12 @@
         <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>28.52</v>
+        <v>27.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B6" t="n">
         <v>4</v>
@@ -528,12 +528,12 @@
         <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>26.94</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B7" t="n">
         <v>8</v>
@@ -545,12 +545,12 @@
         <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>28.59</v>
+        <v>28.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B8" t="n">
         <v>8</v>
@@ -562,12 +562,12 @@
         <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>27.63</v>
+        <v>27.11</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B9" t="n">
         <v>8</v>
@@ -579,12 +579,12 @@
         <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>22</v>
+        <v>21.93</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B10" t="n">
         <v>6</v>
@@ -596,12 +596,12 @@
         <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>33.05</v>
+        <v>32.17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B11" t="n">
         <v>8</v>
@@ -613,12 +613,12 @@
         <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>32.72</v>
+        <v>32.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B12" t="n">
         <v>9</v>
@@ -630,12 +630,12 @@
         <v>51</v>
       </c>
       <c r="E12" t="n">
-        <v>24.43</v>
+        <v>24.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B13" t="n">
         <v>6</v>
@@ -647,12 +647,12 @@
         <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>23.17</v>
+        <v>23.18</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B14" t="n">
         <v>6</v>
@@ -664,12 +664,12 @@
         <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>25</v>
+        <v>24.89</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B15" t="n">
         <v>6</v>
@@ -681,12 +681,12 @@
         <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>23.42</v>
+        <v>23.25</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B16" t="n">
         <v>3</v>
@@ -698,12 +698,12 @@
         <v>57</v>
       </c>
       <c r="E16" t="n">
-        <v>25.51</v>
+        <v>25.55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B17" t="n">
         <v>6</v>
@@ -720,7 +720,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B18" t="n">
         <v>5</v>
@@ -737,7 +737,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B19" t="n">
         <v>8</v>
@@ -754,7 +754,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B20" t="n">
         <v>9</v>
@@ -771,7 +771,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B21" t="n">
         <v>3</v>
@@ -788,7 +788,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B22" t="n">
         <v>5</v>
@@ -805,7 +805,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B23" t="n">
         <v>5</v>
@@ -822,7 +822,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B24" t="n">
         <v>8</v>
@@ -839,7 +839,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B25" t="n">
         <v>7</v>
@@ -856,7 +856,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B26" t="n">
         <v>6</v>
@@ -939,7 +939,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B2" t="n">
         <v>1000000</v>
@@ -971,810 +971,810 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B3" t="n">
-        <v>962081.85</v>
+        <v>894745.09</v>
       </c>
       <c r="C3" t="n">
-        <v>27522.49</v>
+        <v>34687.41</v>
       </c>
       <c r="D3" t="n">
-        <v>8811.290000000001</v>
+        <v>57739.89</v>
       </c>
       <c r="E3" t="n">
-        <v>18711.21</v>
+        <v>-23052.48</v>
       </c>
       <c r="F3" t="n">
-        <v>4128.37</v>
+        <v>5203.11</v>
       </c>
       <c r="G3" t="n">
-        <v>4128.37</v>
+        <v>5203.11</v>
       </c>
       <c r="H3" t="n">
-        <v>-56629.36</v>
+        <v>-82202.42999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>602421.04</v>
+        <v>553079.5699999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B4" t="n">
-        <v>903492.59</v>
+        <v>788685.41</v>
       </c>
       <c r="C4" t="n">
-        <v>1820.54</v>
+        <v>3484.49</v>
       </c>
       <c r="D4" t="n">
-        <v>54986.11</v>
+        <v>125036.39</v>
       </c>
       <c r="E4" t="n">
-        <v>-53165.57</v>
+        <v>-121551.9</v>
       </c>
       <c r="F4" t="n">
-        <v>273.08</v>
+        <v>522.67</v>
       </c>
       <c r="G4" t="n">
-        <v>4401.46</v>
+        <v>5725.78</v>
       </c>
       <c r="H4" t="n">
-        <v>-62053.05</v>
+        <v>-66710.21000000001</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>483569.95</v>
+        <v>395103.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B5" t="n">
-        <v>718294.5699999999</v>
+        <v>607294.77</v>
       </c>
       <c r="C5" t="n">
-        <v>3366.61</v>
+        <v>3636.15</v>
       </c>
       <c r="D5" t="n">
-        <v>54874.59</v>
+        <v>67960.06</v>
       </c>
       <c r="E5" t="n">
-        <v>-51507.98</v>
+        <v>-64323.91</v>
       </c>
       <c r="F5" t="n">
-        <v>504.99</v>
+        <v>545.42</v>
       </c>
       <c r="G5" t="n">
-        <v>4906.45</v>
+        <v>6271.21</v>
       </c>
       <c r="H5" t="n">
-        <v>-195743.09</v>
+        <v>-183776.94</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>381283.31</v>
+        <v>313522.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B6" t="n">
-        <v>861835.83</v>
+        <v>747242.49</v>
       </c>
       <c r="C6" t="n">
-        <v>28481.55</v>
+        <v>31241.4</v>
       </c>
       <c r="D6" t="n">
-        <v>39890.3</v>
+        <v>40774.65</v>
       </c>
       <c r="E6" t="n">
-        <v>-11408.75</v>
+        <v>-9533.26</v>
       </c>
       <c r="F6" t="n">
-        <v>4272.23</v>
+        <v>4686.21</v>
       </c>
       <c r="G6" t="n">
-        <v>9178.68</v>
+        <v>10957.42</v>
       </c>
       <c r="H6" t="n">
-        <v>-40793.07</v>
+        <v>-34295.96</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>491624.72</v>
+        <v>415640.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B7" t="n">
-        <v>940660.6</v>
+        <v>821799.26</v>
       </c>
       <c r="C7" t="n">
-        <v>43719.71</v>
+        <v>48528.85</v>
       </c>
       <c r="D7" t="n">
-        <v>35728.57</v>
+        <v>31201.6</v>
       </c>
       <c r="E7" t="n">
-        <v>7991.14</v>
+        <v>17327.24</v>
       </c>
       <c r="F7" t="n">
-        <v>6557.96</v>
+        <v>7279.33</v>
       </c>
       <c r="G7" t="n">
-        <v>15736.64</v>
+        <v>18236.74</v>
       </c>
       <c r="H7" t="n">
-        <v>30040.55</v>
+        <v>22933.56</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>506858.88</v>
+        <v>446409.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B8" t="n">
-        <v>959438.52</v>
+        <v>837688.46</v>
       </c>
       <c r="C8" t="n">
-        <v>40968.61</v>
+        <v>36010.87</v>
       </c>
       <c r="D8" t="n">
-        <v>37093.42</v>
+        <v>35342.2</v>
       </c>
       <c r="E8" t="n">
-        <v>3875.19</v>
+        <v>668.67</v>
       </c>
       <c r="F8" t="n">
-        <v>6145.29</v>
+        <v>5401.63</v>
       </c>
       <c r="G8" t="n">
-        <v>21881.93</v>
+        <v>23638.37</v>
       </c>
       <c r="H8" t="n">
-        <v>44943.28</v>
+        <v>38154.1</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>548514.76</v>
+        <v>481540.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B9" t="n">
-        <v>1089327.31</v>
+        <v>952479.64</v>
       </c>
       <c r="C9" t="n">
-        <v>43087.56</v>
+        <v>36788.24</v>
       </c>
       <c r="D9" t="n">
-        <v>7810.68</v>
+        <v>9460.200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>35276.88</v>
+        <v>27328.04</v>
       </c>
       <c r="F9" t="n">
-        <v>6463.13</v>
+        <v>5518.24</v>
       </c>
       <c r="G9" t="n">
-        <v>28345.06</v>
+        <v>29156.61</v>
       </c>
       <c r="H9" t="n">
-        <v>139555.19</v>
+        <v>125617.23</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>601936.05</v>
+        <v>516406.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B10" t="n">
-        <v>1205495.33</v>
+        <v>1042307.35</v>
       </c>
       <c r="C10" t="n">
-        <v>87131.31</v>
+        <v>82996.98</v>
       </c>
       <c r="D10" t="n">
-        <v>11736.94</v>
+        <v>17992.89</v>
       </c>
       <c r="E10" t="n">
-        <v>75394.37</v>
+        <v>65004.09</v>
       </c>
       <c r="F10" t="n">
-        <v>13069.7</v>
+        <v>12449.55</v>
       </c>
       <c r="G10" t="n">
-        <v>41414.76</v>
+        <v>41606.16</v>
       </c>
       <c r="H10" t="n">
-        <v>180328.84</v>
+        <v>150440.84</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>530522.3199999999</v>
+        <v>457139.93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B11" t="n">
-        <v>876110.4</v>
+        <v>733288.76</v>
       </c>
       <c r="C11" t="n">
-        <v>60682.99</v>
+        <v>54128.13</v>
       </c>
       <c r="D11" t="n">
-        <v>88346.74000000001</v>
+        <v>99360.02</v>
       </c>
       <c r="E11" t="n">
-        <v>-27663.75</v>
+        <v>-45231.89</v>
       </c>
       <c r="F11" t="n">
-        <v>9102.450000000001</v>
+        <v>8119.22</v>
       </c>
       <c r="G11" t="n">
-        <v>50517.21</v>
+        <v>49725.38</v>
       </c>
       <c r="H11" t="n">
-        <v>-121392.34</v>
+        <v>-113345.86</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>579052.59</v>
+        <v>471798.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>1017337.9</v>
+        <v>857779.1899999999</v>
       </c>
       <c r="C12" t="n">
-        <v>55989.47</v>
+        <v>49726.35</v>
       </c>
       <c r="D12" t="n">
-        <v>31216.45</v>
+        <v>27735.33</v>
       </c>
       <c r="E12" t="n">
-        <v>24773.02</v>
+        <v>21991.03</v>
       </c>
       <c r="F12" t="n">
-        <v>8398.42</v>
+        <v>7458.95</v>
       </c>
       <c r="G12" t="n">
-        <v>58915.63</v>
+        <v>57184.33</v>
       </c>
       <c r="H12" t="n">
-        <v>-4937.86</v>
+        <v>-10846.45</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>665755.9</v>
+        <v>562858.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>1111598.05</v>
+        <v>936682.89</v>
       </c>
       <c r="C13" t="n">
-        <v>33906.39</v>
+        <v>28642.86</v>
       </c>
       <c r="D13" t="n">
-        <v>38690.52</v>
+        <v>39017.56</v>
       </c>
       <c r="E13" t="n">
-        <v>-4784.13</v>
+        <v>-10374.7</v>
       </c>
       <c r="F13" t="n">
-        <v>5085.96</v>
+        <v>4296.43</v>
       </c>
       <c r="G13" t="n">
-        <v>64001.59</v>
+        <v>61480.76</v>
       </c>
       <c r="H13" t="n">
-        <v>94106.42999999999</v>
+        <v>78431.95</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>543156.97</v>
+        <v>455930.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B14" t="n">
-        <v>1139508.05</v>
+        <v>959971.22</v>
       </c>
       <c r="C14" t="n">
-        <v>46752.35</v>
+        <v>39440.95</v>
       </c>
       <c r="D14" t="n">
-        <v>8893.35</v>
+        <v>7633.5</v>
       </c>
       <c r="E14" t="n">
-        <v>37859</v>
+        <v>31807.45</v>
       </c>
       <c r="F14" t="n">
-        <v>7012.85</v>
+        <v>5916.14</v>
       </c>
       <c r="G14" t="n">
-        <v>71014.44</v>
+        <v>67396.89999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>84157.42999999999</v>
+        <v>69912.83</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>528003.5699999999</v>
+        <v>445075.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B15" t="n">
-        <v>1324644.88</v>
+        <v>1117895.68</v>
       </c>
       <c r="C15" t="n">
-        <v>82232.31</v>
+        <v>69252.85000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>8528.290000000001</v>
+        <v>7728.86</v>
       </c>
       <c r="E15" t="n">
-        <v>73704.02</v>
+        <v>61524</v>
       </c>
       <c r="F15" t="n">
-        <v>12334.85</v>
+        <v>10387.93</v>
       </c>
       <c r="G15" t="n">
-        <v>83349.28999999999</v>
+        <v>77784.83</v>
       </c>
       <c r="H15" t="n">
-        <v>195590.24</v>
+        <v>166313.3</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>662264</v>
+        <v>556420.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B16" t="n">
-        <v>1696875.35</v>
+        <v>1439807.23</v>
       </c>
       <c r="C16" t="n">
-        <v>125550.83</v>
+        <v>108047.63</v>
       </c>
       <c r="D16" t="n">
-        <v>13764.83</v>
+        <v>12487.55</v>
       </c>
       <c r="E16" t="n">
-        <v>111785.99</v>
+        <v>95560.08</v>
       </c>
       <c r="F16" t="n">
-        <v>18832.62</v>
+        <v>16207.15</v>
       </c>
       <c r="G16" t="n">
-        <v>102181.91</v>
+        <v>93991.97</v>
       </c>
       <c r="H16" t="n">
-        <v>456034.71</v>
+        <v>392664.77</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>794902.84</v>
+        <v>669591.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B17" t="n">
-        <v>1961917.78</v>
+        <v>1666503.48</v>
       </c>
       <c r="C17" t="n">
-        <v>210412.23</v>
+        <v>186545.43</v>
       </c>
       <c r="D17" t="n">
-        <v>24162.34</v>
+        <v>20750.29</v>
       </c>
       <c r="E17" t="n">
-        <v>186249.89</v>
+        <v>165795.14</v>
       </c>
       <c r="F17" t="n">
-        <v>31561.83</v>
+        <v>27981.81</v>
       </c>
       <c r="G17" t="n">
-        <v>133743.74</v>
+        <v>121973.79</v>
       </c>
       <c r="H17" t="n">
-        <v>534827.25</v>
+        <v>453565.88</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1001094.91</v>
+        <v>851584.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B18" t="n">
-        <v>2078540.64</v>
+        <v>1765565.94</v>
       </c>
       <c r="C18" t="n">
-        <v>142431.7</v>
+        <v>120837.08</v>
       </c>
       <c r="D18" t="n">
-        <v>1967.73</v>
+        <v>1675.55</v>
       </c>
       <c r="E18" t="n">
-        <v>140463.97</v>
+        <v>119161.54</v>
       </c>
       <c r="F18" t="n">
-        <v>21364.75</v>
+        <v>18125.56</v>
       </c>
       <c r="G18" t="n">
-        <v>155108.5</v>
+        <v>140099.35</v>
       </c>
       <c r="H18" t="n">
-        <v>510986.15</v>
+        <v>433466.8</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1093110.5</v>
+        <v>928516.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B19" t="n">
-        <v>2346939.82</v>
+        <v>1993551.11</v>
       </c>
       <c r="C19" t="n">
-        <v>201571.38</v>
+        <v>171407.01</v>
       </c>
       <c r="D19" t="n">
-        <v>8482.24</v>
+        <v>7205.03</v>
       </c>
       <c r="E19" t="n">
-        <v>193089.14</v>
+        <v>164201.98</v>
       </c>
       <c r="F19" t="n">
-        <v>30235.71</v>
+        <v>25711.05</v>
       </c>
       <c r="G19" t="n">
-        <v>185344.21</v>
+        <v>165810.4</v>
       </c>
       <c r="H19" t="n">
-        <v>586296.1800000001</v>
+        <v>497249.99</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1170108.78</v>
+        <v>993920.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B20" t="n">
-        <v>2871803.42</v>
+        <v>2439383.77</v>
       </c>
       <c r="C20" t="n">
-        <v>216016.4</v>
+        <v>183184.78</v>
       </c>
       <c r="D20" t="n">
-        <v>9174.34</v>
+        <v>7798.88</v>
       </c>
       <c r="E20" t="n">
-        <v>206842.06</v>
+        <v>175385.9</v>
       </c>
       <c r="F20" t="n">
-        <v>32402.46</v>
+        <v>27477.72</v>
       </c>
       <c r="G20" t="n">
-        <v>217746.67</v>
+        <v>193288.12</v>
       </c>
       <c r="H20" t="n">
-        <v>904317.72</v>
+        <v>767696.76</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1271967.35</v>
+        <v>1080441.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B21" t="n">
-        <v>2799026.89</v>
+        <v>2377565.51</v>
       </c>
       <c r="C21" t="n">
-        <v>263765.7</v>
+        <v>224032.29</v>
       </c>
       <c r="D21" t="n">
-        <v>68602.3</v>
+        <v>58311.09</v>
       </c>
       <c r="E21" t="n">
-        <v>195163.41</v>
+        <v>165721.2</v>
       </c>
       <c r="F21" t="n">
-        <v>39564.86</v>
+        <v>33604.84</v>
       </c>
       <c r="G21" t="n">
-        <v>257311.52</v>
+        <v>226892.96</v>
       </c>
       <c r="H21" t="n">
-        <v>636377.78</v>
+        <v>540157.29</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1766873.09</v>
+        <v>1500827.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B22" t="n">
-        <v>3715580.34</v>
+        <v>3156109.62</v>
       </c>
       <c r="C22" t="n">
-        <v>336224.49</v>
+        <v>285583.66</v>
       </c>
       <c r="D22" t="n">
-        <v>13815.84</v>
+        <v>11735.53</v>
       </c>
       <c r="E22" t="n">
-        <v>322408.65</v>
+        <v>273848.13</v>
       </c>
       <c r="F22" t="n">
-        <v>50433.67</v>
+        <v>42837.55</v>
       </c>
       <c r="G22" t="n">
-        <v>307745.19</v>
+        <v>269730.51</v>
       </c>
       <c r="H22" t="n">
-        <v>1230522.58</v>
+        <v>1044853.27</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1535691.21</v>
+        <v>1304455.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B23" t="n">
-        <v>4350591.54</v>
+        <v>3695504.48</v>
       </c>
       <c r="C23" t="n">
-        <v>314728.06</v>
+        <v>267327.71</v>
       </c>
       <c r="D23" t="n">
-        <v>27548.99</v>
+        <v>23400.82</v>
       </c>
       <c r="E23" t="n">
-        <v>287179.07</v>
+        <v>243926.89</v>
       </c>
       <c r="F23" t="n">
-        <v>47209.21</v>
+        <v>40099.16</v>
       </c>
       <c r="G23" t="n">
-        <v>354954.4</v>
+        <v>309829.67</v>
       </c>
       <c r="H23" t="n">
-        <v>1578354.71</v>
+        <v>1340321.24</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1760863.58</v>
+        <v>1495722.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B24" t="n">
-        <v>5620013.95</v>
+        <v>4773784.57</v>
       </c>
       <c r="C24" t="n">
-        <v>559486.42</v>
+        <v>475242.18</v>
       </c>
       <c r="D24" t="n">
-        <v>930.02</v>
+        <v>789.98</v>
       </c>
       <c r="E24" t="n">
-        <v>558556.41</v>
+        <v>474452.19</v>
       </c>
       <c r="F24" t="n">
-        <v>83922.96000000001</v>
+        <v>71286.33</v>
       </c>
       <c r="G24" t="n">
-        <v>438877.37</v>
+        <v>381115.99</v>
       </c>
       <c r="H24" t="n">
-        <v>2289220.72</v>
+        <v>1944149.13</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2464677.67</v>
+        <v>2093560.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B25" t="n">
-        <v>4580436.91</v>
+        <v>3890741.06</v>
       </c>
       <c r="C25" t="n">
-        <v>395684.46</v>
+        <v>336022.47</v>
       </c>
       <c r="D25" t="n">
-        <v>82014.81</v>
+        <v>69665.49000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>313669.65</v>
+        <v>266356.98</v>
       </c>
       <c r="F25" t="n">
-        <v>59352.67</v>
+        <v>50403.37</v>
       </c>
       <c r="G25" t="n">
-        <v>498230.04</v>
+        <v>431519.37</v>
       </c>
       <c r="H25" t="n">
-        <v>935974.03</v>
+        <v>794748.65</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2351765.32</v>
+        <v>1997650.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="n">
-        <v>5991355.49</v>
+        <v>5089211.64</v>
       </c>
       <c r="C26" t="n">
-        <v>386728.06</v>
+        <v>328349.14</v>
       </c>
       <c r="D26" t="n">
-        <v>56287.56</v>
+        <v>47812.1</v>
       </c>
       <c r="E26" t="n">
-        <v>330440.5</v>
+        <v>280537.04</v>
       </c>
       <c r="F26" t="n">
-        <v>58009.21</v>
+        <v>49252.37</v>
       </c>
       <c r="G26" t="n">
-        <v>556239.25</v>
+        <v>480771.74</v>
       </c>
       <c r="H26" t="n">
-        <v>2016452.1</v>
+        <v>1712682.18</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2739487.95</v>
+        <v>2326991.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B27" t="n">
-        <v>7649632.08</v>
+        <v>6497794.47</v>
       </c>
       <c r="C27" t="n">
-        <v>562390.66</v>
+        <v>477654.25</v>
       </c>
       <c r="D27" t="n">
-        <v>60757.32</v>
+        <v>51608.83</v>
       </c>
       <c r="E27" t="n">
-        <v>501633.34</v>
+        <v>426045.42</v>
       </c>
       <c r="F27" t="n">
-        <v>84358.60000000001</v>
+        <v>71648.14</v>
       </c>
       <c r="G27" t="n">
-        <v>640597.84</v>
+        <v>552419.87</v>
       </c>
       <c r="H27" t="n">
-        <v>3173095.35</v>
+        <v>2695219.59</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3038826.48</v>
+        <v>2581257.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="n">
-        <v>9153084.17</v>
+        <v>7774865.39</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>640597.84</v>
+        <v>552419.87</v>
       </c>
       <c r="H28" t="n">
-        <v>4676547.44</v>
+        <v>3972290.51</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1869,7 +1869,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="B2" t="n">
         <v>1000000</v>
@@ -1901,810 +1901,810 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="B3" t="n">
-        <v>962081.85</v>
+        <v>894745.09</v>
       </c>
       <c r="C3" t="n">
-        <v>27522.49</v>
+        <v>34687.41</v>
       </c>
       <c r="D3" t="n">
-        <v>8811.290000000001</v>
+        <v>57739.89</v>
       </c>
       <c r="E3" t="n">
-        <v>18711.21</v>
+        <v>-23052.48</v>
       </c>
       <c r="F3" t="n">
-        <v>2806.68</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>2806.68</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-56629.36</v>
+        <v>-82202.42999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>23052.48</v>
       </c>
       <c r="J3" t="n">
-        <v>602421.04</v>
+        <v>553079.5699999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B4" t="n">
-        <v>903492.59</v>
+        <v>788685.41</v>
       </c>
       <c r="C4" t="n">
-        <v>1820.54</v>
+        <v>3484.49</v>
       </c>
       <c r="D4" t="n">
-        <v>54986.11</v>
+        <v>125036.39</v>
       </c>
       <c r="E4" t="n">
-        <v>-53165.57</v>
+        <v>-121551.9</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>2806.68</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-62053.05</v>
+        <v>-66710.21000000001</v>
       </c>
       <c r="I4" t="n">
-        <v>53165.57</v>
+        <v>144604.38</v>
       </c>
       <c r="J4" t="n">
-        <v>483569.95</v>
+        <v>395103.99</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="B5" t="n">
-        <v>718294.5699999999</v>
+        <v>607294.77</v>
       </c>
       <c r="C5" t="n">
-        <v>3366.61</v>
+        <v>3636.15</v>
       </c>
       <c r="D5" t="n">
-        <v>54874.59</v>
+        <v>67960.06</v>
       </c>
       <c r="E5" t="n">
-        <v>-51507.98</v>
+        <v>-64323.91</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>2806.68</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-195743.09</v>
+        <v>-183776.94</v>
       </c>
       <c r="I5" t="n">
-        <v>104673.55</v>
+        <v>208928.29</v>
       </c>
       <c r="J5" t="n">
-        <v>381283.31</v>
+        <v>313522.81</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="B6" t="n">
-        <v>861835.83</v>
+        <v>747242.49</v>
       </c>
       <c r="C6" t="n">
-        <v>28481.55</v>
+        <v>31241.4</v>
       </c>
       <c r="D6" t="n">
-        <v>39890.3</v>
+        <v>40774.65</v>
       </c>
       <c r="E6" t="n">
-        <v>-11408.75</v>
+        <v>-9533.26</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2806.68</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-40793.07</v>
+        <v>-34295.96</v>
       </c>
       <c r="I6" t="n">
-        <v>116082.3</v>
+        <v>218461.55</v>
       </c>
       <c r="J6" t="n">
-        <v>491624.72</v>
+        <v>415640.3</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B7" t="n">
-        <v>940660.6</v>
+        <v>821799.26</v>
       </c>
       <c r="C7" t="n">
-        <v>43719.71</v>
+        <v>48528.85</v>
       </c>
       <c r="D7" t="n">
-        <v>35728.57</v>
+        <v>31201.6</v>
       </c>
       <c r="E7" t="n">
-        <v>7991.14</v>
+        <v>17327.24</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>2806.68</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>30040.55</v>
+        <v>22933.56</v>
       </c>
       <c r="I7" t="n">
-        <v>108091.16</v>
+        <v>201134.31</v>
       </c>
       <c r="J7" t="n">
-        <v>506858.88</v>
+        <v>446409.38</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B8" t="n">
-        <v>959438.52</v>
+        <v>837688.46</v>
       </c>
       <c r="C8" t="n">
-        <v>40968.61</v>
+        <v>36010.87</v>
       </c>
       <c r="D8" t="n">
-        <v>37093.42</v>
+        <v>35342.2</v>
       </c>
       <c r="E8" t="n">
-        <v>3875.19</v>
+        <v>668.67</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>2806.68</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>44943.28</v>
+        <v>38154.1</v>
       </c>
       <c r="I8" t="n">
-        <v>104215.97</v>
+        <v>200465.63</v>
       </c>
       <c r="J8" t="n">
-        <v>548514.76</v>
+        <v>481540.87</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B9" t="n">
-        <v>1089327.31</v>
+        <v>952479.64</v>
       </c>
       <c r="C9" t="n">
-        <v>43087.56</v>
+        <v>36788.24</v>
       </c>
       <c r="D9" t="n">
-        <v>7810.68</v>
+        <v>9460.200000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>35276.88</v>
+        <v>27328.04</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>2806.68</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>139555.19</v>
+        <v>125617.23</v>
       </c>
       <c r="I9" t="n">
-        <v>68939.09</v>
+        <v>173137.59</v>
       </c>
       <c r="J9" t="n">
-        <v>601936.05</v>
+        <v>516406.76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B10" t="n">
-        <v>1205495.33</v>
+        <v>1042307.35</v>
       </c>
       <c r="C10" t="n">
-        <v>87131.31</v>
+        <v>82996.98</v>
       </c>
       <c r="D10" t="n">
-        <v>11736.94</v>
+        <v>17992.89</v>
       </c>
       <c r="E10" t="n">
-        <v>75394.37</v>
+        <v>65004.09</v>
       </c>
       <c r="F10" t="n">
-        <v>968.29</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>3774.97</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>180328.84</v>
+        <v>150440.84</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>108133.5</v>
       </c>
       <c r="J10" t="n">
-        <v>530522.3199999999</v>
+        <v>457139.93</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B11" t="n">
-        <v>876110.4</v>
+        <v>733288.76</v>
       </c>
       <c r="C11" t="n">
-        <v>60682.99</v>
+        <v>54128.13</v>
       </c>
       <c r="D11" t="n">
-        <v>88346.74000000001</v>
+        <v>99360.02</v>
       </c>
       <c r="E11" t="n">
-        <v>-27663.75</v>
+        <v>-45231.89</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>3774.97</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-121392.34</v>
+        <v>-113345.86</v>
       </c>
       <c r="I11" t="n">
-        <v>27663.75</v>
+        <v>153365.39</v>
       </c>
       <c r="J11" t="n">
-        <v>579052.59</v>
+        <v>471798.78</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>1017337.9</v>
+        <v>857779.1899999999</v>
       </c>
       <c r="C12" t="n">
-        <v>55989.47</v>
+        <v>49726.35</v>
       </c>
       <c r="D12" t="n">
-        <v>31216.45</v>
+        <v>27735.33</v>
       </c>
       <c r="E12" t="n">
-        <v>24773.02</v>
+        <v>21991.03</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3774.97</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-4937.86</v>
+        <v>-10846.45</v>
       </c>
       <c r="I12" t="n">
-        <v>2890.72</v>
+        <v>131374.36</v>
       </c>
       <c r="J12" t="n">
-        <v>665755.9</v>
+        <v>562858.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>1111598.05</v>
+        <v>936682.89</v>
       </c>
       <c r="C13" t="n">
-        <v>33906.39</v>
+        <v>28642.86</v>
       </c>
       <c r="D13" t="n">
-        <v>38690.52</v>
+        <v>39017.56</v>
       </c>
       <c r="E13" t="n">
-        <v>-4784.13</v>
+        <v>-10374.7</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>3774.97</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>94106.42999999999</v>
+        <v>78431.95</v>
       </c>
       <c r="I13" t="n">
-        <v>7674.86</v>
+        <v>141749.06</v>
       </c>
       <c r="J13" t="n">
-        <v>543156.97</v>
+        <v>455930.16</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B14" t="n">
-        <v>1139508.05</v>
+        <v>959971.22</v>
       </c>
       <c r="C14" t="n">
-        <v>46752.35</v>
+        <v>39440.95</v>
       </c>
       <c r="D14" t="n">
-        <v>8893.35</v>
+        <v>7633.5</v>
       </c>
       <c r="E14" t="n">
-        <v>37859</v>
+        <v>31807.45</v>
       </c>
       <c r="F14" t="n">
-        <v>4527.62</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>8302.59</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>84157.42999999999</v>
+        <v>69912.83</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>109941.61</v>
       </c>
       <c r="J14" t="n">
-        <v>528003.5699999999</v>
+        <v>445075.72</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B15" t="n">
-        <v>1324644.88</v>
+        <v>1117895.68</v>
       </c>
       <c r="C15" t="n">
-        <v>82232.31</v>
+        <v>69252.85000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>8528.290000000001</v>
+        <v>7728.86</v>
       </c>
       <c r="E15" t="n">
-        <v>73704.02</v>
+        <v>61524</v>
       </c>
       <c r="F15" t="n">
-        <v>11055.6</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>19358.2</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>195590.24</v>
+        <v>166313.3</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>48417.62</v>
       </c>
       <c r="J15" t="n">
-        <v>662264</v>
+        <v>556420.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B16" t="n">
-        <v>1696875.35</v>
+        <v>1439807.23</v>
       </c>
       <c r="C16" t="n">
-        <v>125550.83</v>
+        <v>108047.63</v>
       </c>
       <c r="D16" t="n">
-        <v>13764.83</v>
+        <v>12487.55</v>
       </c>
       <c r="E16" t="n">
-        <v>111785.99</v>
+        <v>95560.08</v>
       </c>
       <c r="F16" t="n">
-        <v>16767.9</v>
+        <v>7071.37</v>
       </c>
       <c r="G16" t="n">
-        <v>36126.1</v>
+        <v>7071.37</v>
       </c>
       <c r="H16" t="n">
-        <v>456034.71</v>
+        <v>392664.77</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>794902.84</v>
+        <v>669591.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B17" t="n">
-        <v>1961917.78</v>
+        <v>1666503.48</v>
       </c>
       <c r="C17" t="n">
-        <v>210412.23</v>
+        <v>186545.43</v>
       </c>
       <c r="D17" t="n">
-        <v>24162.34</v>
+        <v>20750.29</v>
       </c>
       <c r="E17" t="n">
-        <v>186249.89</v>
+        <v>165795.14</v>
       </c>
       <c r="F17" t="n">
-        <v>27937.48</v>
+        <v>24869.27</v>
       </c>
       <c r="G17" t="n">
-        <v>64063.58</v>
+        <v>31940.64</v>
       </c>
       <c r="H17" t="n">
-        <v>534827.25</v>
+        <v>453565.88</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>1001094.91</v>
+        <v>851584.41</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B18" t="n">
-        <v>2078540.64</v>
+        <v>1765565.94</v>
       </c>
       <c r="C18" t="n">
-        <v>142431.7</v>
+        <v>120837.08</v>
       </c>
       <c r="D18" t="n">
-        <v>1967.73</v>
+        <v>1675.55</v>
       </c>
       <c r="E18" t="n">
-        <v>140463.97</v>
+        <v>119161.54</v>
       </c>
       <c r="F18" t="n">
-        <v>21069.59</v>
+        <v>17874.23</v>
       </c>
       <c r="G18" t="n">
-        <v>85133.17</v>
+        <v>49814.87</v>
       </c>
       <c r="H18" t="n">
-        <v>510986.15</v>
+        <v>433466.8</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>1093110.5</v>
+        <v>928516.2</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B19" t="n">
-        <v>2346939.82</v>
+        <v>1993551.11</v>
       </c>
       <c r="C19" t="n">
-        <v>201571.38</v>
+        <v>171407.01</v>
       </c>
       <c r="D19" t="n">
-        <v>8482.24</v>
+        <v>7205.03</v>
       </c>
       <c r="E19" t="n">
-        <v>193089.14</v>
+        <v>164201.98</v>
       </c>
       <c r="F19" t="n">
-        <v>28963.37</v>
+        <v>24630.3</v>
       </c>
       <c r="G19" t="n">
-        <v>114096.54</v>
+        <v>74445.17</v>
       </c>
       <c r="H19" t="n">
-        <v>586296.1800000001</v>
+        <v>497249.99</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1170108.78</v>
+        <v>993920.53</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B20" t="n">
-        <v>2871803.42</v>
+        <v>2439383.77</v>
       </c>
       <c r="C20" t="n">
-        <v>216016.4</v>
+        <v>183184.78</v>
       </c>
       <c r="D20" t="n">
-        <v>9174.34</v>
+        <v>7798.88</v>
       </c>
       <c r="E20" t="n">
-        <v>206842.06</v>
+        <v>175385.9</v>
       </c>
       <c r="F20" t="n">
-        <v>31026.31</v>
+        <v>26307.88</v>
       </c>
       <c r="G20" t="n">
-        <v>145122.85</v>
+        <v>100753.05</v>
       </c>
       <c r="H20" t="n">
-        <v>904317.72</v>
+        <v>767696.76</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1271967.35</v>
+        <v>1080441.82</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B21" t="n">
-        <v>2799026.89</v>
+        <v>2377565.51</v>
       </c>
       <c r="C21" t="n">
-        <v>263765.7</v>
+        <v>224032.29</v>
       </c>
       <c r="D21" t="n">
-        <v>68602.3</v>
+        <v>58311.09</v>
       </c>
       <c r="E21" t="n">
-        <v>195163.41</v>
+        <v>165721.2</v>
       </c>
       <c r="F21" t="n">
-        <v>29274.51</v>
+        <v>24858.18</v>
       </c>
       <c r="G21" t="n">
-        <v>174397.37</v>
+        <v>125611.23</v>
       </c>
       <c r="H21" t="n">
-        <v>636377.78</v>
+        <v>540157.29</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1766873.09</v>
+        <v>1500827.5</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B22" t="n">
-        <v>3715580.34</v>
+        <v>3156109.62</v>
       </c>
       <c r="C22" t="n">
-        <v>336224.49</v>
+        <v>285583.66</v>
       </c>
       <c r="D22" t="n">
-        <v>13815.84</v>
+        <v>11735.53</v>
       </c>
       <c r="E22" t="n">
-        <v>322408.65</v>
+        <v>273848.13</v>
       </c>
       <c r="F22" t="n">
-        <v>48361.3</v>
+        <v>41077.22</v>
       </c>
       <c r="G22" t="n">
-        <v>222758.66</v>
+        <v>166688.45</v>
       </c>
       <c r="H22" t="n">
-        <v>1230522.58</v>
+        <v>1044853.27</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1535691.21</v>
+        <v>1304455.66</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="B23" t="n">
-        <v>4350591.54</v>
+        <v>3695504.48</v>
       </c>
       <c r="C23" t="n">
-        <v>314728.06</v>
+        <v>267327.71</v>
       </c>
       <c r="D23" t="n">
-        <v>27548.99</v>
+        <v>23400.82</v>
       </c>
       <c r="E23" t="n">
-        <v>287179.07</v>
+        <v>243926.89</v>
       </c>
       <c r="F23" t="n">
-        <v>43076.86</v>
+        <v>36589.03</v>
       </c>
       <c r="G23" t="n">
-        <v>265835.52</v>
+        <v>203277.49</v>
       </c>
       <c r="H23" t="n">
-        <v>1578354.71</v>
+        <v>1340321.24</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1760863.58</v>
+        <v>1495722.86</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="B24" t="n">
-        <v>5620013.95</v>
+        <v>4773784.57</v>
       </c>
       <c r="C24" t="n">
-        <v>559486.42</v>
+        <v>475242.18</v>
       </c>
       <c r="D24" t="n">
-        <v>930.02</v>
+        <v>789.98</v>
       </c>
       <c r="E24" t="n">
-        <v>558556.41</v>
+        <v>474452.19</v>
       </c>
       <c r="F24" t="n">
-        <v>83783.46000000001</v>
+        <v>71167.83</v>
       </c>
       <c r="G24" t="n">
-        <v>349618.98</v>
+        <v>274445.32</v>
       </c>
       <c r="H24" t="n">
-        <v>2289220.72</v>
+        <v>1944149.13</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2464677.67</v>
+        <v>2093560.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="B25" t="n">
-        <v>4580436.91</v>
+        <v>3890741.06</v>
       </c>
       <c r="C25" t="n">
-        <v>395684.46</v>
+        <v>336022.47</v>
       </c>
       <c r="D25" t="n">
-        <v>82014.81</v>
+        <v>69665.49000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>313669.65</v>
+        <v>266356.98</v>
       </c>
       <c r="F25" t="n">
-        <v>47050.45</v>
+        <v>39953.55</v>
       </c>
       <c r="G25" t="n">
-        <v>396669.43</v>
+        <v>314398.86</v>
       </c>
       <c r="H25" t="n">
-        <v>935974.03</v>
+        <v>794748.65</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>2351765.32</v>
+        <v>1997650.02</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="B26" t="n">
-        <v>5991355.49</v>
+        <v>5089211.64</v>
       </c>
       <c r="C26" t="n">
-        <v>386728.06</v>
+        <v>328349.14</v>
       </c>
       <c r="D26" t="n">
-        <v>56287.56</v>
+        <v>47812.1</v>
       </c>
       <c r="E26" t="n">
-        <v>330440.5</v>
+        <v>280537.04</v>
       </c>
       <c r="F26" t="n">
-        <v>49566.08</v>
+        <v>42080.56</v>
       </c>
       <c r="G26" t="n">
-        <v>446235.51</v>
+        <v>356479.42</v>
       </c>
       <c r="H26" t="n">
-        <v>2016452.1</v>
+        <v>1712682.18</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2739487.95</v>
+        <v>2326991.61</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="B27" t="n">
-        <v>7649632.08</v>
+        <v>6497794.47</v>
       </c>
       <c r="C27" t="n">
-        <v>562390.66</v>
+        <v>477654.25</v>
       </c>
       <c r="D27" t="n">
-        <v>60757.32</v>
+        <v>51608.83</v>
       </c>
       <c r="E27" t="n">
-        <v>501633.34</v>
+        <v>426045.42</v>
       </c>
       <c r="F27" t="n">
-        <v>75245</v>
+        <v>63906.81</v>
       </c>
       <c r="G27" t="n">
-        <v>521480.51</v>
+        <v>420386.23</v>
       </c>
       <c r="H27" t="n">
-        <v>3173095.35</v>
+        <v>2695219.59</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>3038826.48</v>
+        <v>2581257.46</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="B28" t="n">
-        <v>9153084.17</v>
+        <v>7774865.39</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>521480.51</v>
+        <v>420386.23</v>
       </c>
       <c r="H28" t="n">
-        <v>4676547.44</v>
+        <v>3972290.51</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$9,153,084</t>
+          <t>$7,774,865</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>815.3%</t>
+          <t>677.5%</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$4,270,652</t>
+          <t>$3,682,799</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$794,116</t>
+          <t>$880,224</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$640,598</t>
+          <t>$552,420</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$521,481</t>
+          <t>$420,386</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$119,117</t>
+          <t>$132,034</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25.7%</t>
+          <t>25.5%</t>
         </is>
       </c>
     </row>

--- a/results-excel/turnover_tax_analysis.xlsx
+++ b/results-excel/turnover_tax_analysis.xlsx
@@ -460,7 +460,7 @@
         <v>50</v>
       </c>
       <c r="E2" t="n">
-        <v>30.91</v>
+        <v>30.56</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         <v>51</v>
       </c>
       <c r="E3" t="n">
-        <v>25.05</v>
+        <v>25.18</v>
       </c>
     </row>
     <row r="4">
@@ -494,7 +494,7 @@
         <v>51</v>
       </c>
       <c r="E4" t="n">
-        <v>25.81</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="5">
@@ -511,7 +511,7 @@
         <v>53</v>
       </c>
       <c r="E5" t="n">
-        <v>27.81</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="6">
@@ -528,7 +528,7 @@
         <v>56</v>
       </c>
       <c r="E6" t="n">
-        <v>27.16</v>
+        <v>27.02</v>
       </c>
     </row>
     <row r="7">
@@ -545,7 +545,7 @@
         <v>52</v>
       </c>
       <c r="E7" t="n">
-        <v>28.74</v>
+        <v>28.53</v>
       </c>
     </row>
     <row r="8">
@@ -562,7 +562,7 @@
         <v>52</v>
       </c>
       <c r="E8" t="n">
-        <v>27.11</v>
+        <v>27.13</v>
       </c>
     </row>
     <row r="9">
@@ -579,7 +579,7 @@
         <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>21.93</v>
+        <v>20.61</v>
       </c>
     </row>
     <row r="10">
@@ -596,7 +596,7 @@
         <v>54</v>
       </c>
       <c r="E10" t="n">
-        <v>32.17</v>
+        <v>30.77</v>
       </c>
     </row>
     <row r="11">
@@ -613,7 +613,7 @@
         <v>52</v>
       </c>
       <c r="E11" t="n">
-        <v>32.81</v>
+        <v>32.72</v>
       </c>
     </row>
     <row r="12">
@@ -647,7 +647,7 @@
         <v>54</v>
       </c>
       <c r="E13" t="n">
-        <v>23.18</v>
+        <v>23.06</v>
       </c>
     </row>
     <row r="14">
@@ -664,7 +664,7 @@
         <v>54</v>
       </c>
       <c r="E14" t="n">
-        <v>24.89</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="15">
@@ -681,7 +681,7 @@
         <v>54</v>
       </c>
       <c r="E15" t="n">
-        <v>23.25</v>
+        <v>23.45</v>
       </c>
     </row>
     <row r="16">
@@ -698,7 +698,7 @@
         <v>57</v>
       </c>
       <c r="E16" t="n">
-        <v>25.55</v>
+        <v>25.03</v>
       </c>
     </row>
     <row r="17">
@@ -715,7 +715,7 @@
         <v>54</v>
       </c>
       <c r="E17" t="n">
-        <v>26.3</v>
+        <v>26.51</v>
       </c>
     </row>
     <row r="18">
@@ -732,7 +732,7 @@
         <v>55</v>
       </c>
       <c r="E18" t="n">
-        <v>24.93</v>
+        <v>24.94</v>
       </c>
     </row>
     <row r="19">
@@ -749,7 +749,7 @@
         <v>52</v>
       </c>
       <c r="E19" t="n">
-        <v>22.15</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="20">
@@ -766,7 +766,7 @@
         <v>51</v>
       </c>
       <c r="E20" t="n">
-        <v>31.56</v>
+        <v>31.7</v>
       </c>
     </row>
     <row r="21">
@@ -783,7 +783,7 @@
         <v>57</v>
       </c>
       <c r="E21" t="n">
-        <v>20.67</v>
+        <v>20.53</v>
       </c>
     </row>
     <row r="22">
@@ -800,7 +800,7 @@
         <v>55</v>
       </c>
       <c r="E22" t="n">
-        <v>20.24</v>
+        <v>20.1</v>
       </c>
     </row>
     <row r="23">
@@ -817,7 +817,7 @@
         <v>55</v>
       </c>
       <c r="E23" t="n">
-        <v>21.93</v>
+        <v>21.71</v>
       </c>
     </row>
     <row r="24">
@@ -834,7 +834,7 @@
         <v>52</v>
       </c>
       <c r="E24" t="n">
-        <v>25.67</v>
+        <v>25.36</v>
       </c>
     </row>
     <row r="25">
@@ -851,7 +851,7 @@
         <v>53</v>
       </c>
       <c r="E25" t="n">
-        <v>22.86</v>
+        <v>22.29</v>
       </c>
     </row>
     <row r="26">
@@ -868,7 +868,7 @@
         <v>54</v>
       </c>
       <c r="E26" t="n">
-        <v>19.86</v>
+        <v>20.1</v>
       </c>
     </row>
   </sheetData>
@@ -974,31 +974,31 @@
         <v>2001</v>
       </c>
       <c r="B3" t="n">
-        <v>894745.09</v>
+        <v>873104</v>
       </c>
       <c r="C3" t="n">
-        <v>34687.41</v>
+        <v>23433.16</v>
       </c>
       <c r="D3" t="n">
-        <v>57739.89</v>
+        <v>59839.72</v>
       </c>
       <c r="E3" t="n">
-        <v>-23052.48</v>
+        <v>-36406.57</v>
       </c>
       <c r="F3" t="n">
-        <v>5203.11</v>
+        <v>3514.97</v>
       </c>
       <c r="G3" t="n">
-        <v>5203.11</v>
+        <v>3514.97</v>
       </c>
       <c r="H3" t="n">
-        <v>-82202.42999999999</v>
+        <v>-90489.42999999999</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>553079.5699999999</v>
+        <v>533680.6800000001</v>
       </c>
     </row>
     <row r="4">
@@ -1006,31 +1006,31 @@
         <v>2002</v>
       </c>
       <c r="B4" t="n">
-        <v>788685.41</v>
+        <v>752731.6899999999</v>
       </c>
       <c r="C4" t="n">
-        <v>3484.49</v>
+        <v>3501.53</v>
       </c>
       <c r="D4" t="n">
-        <v>125036.39</v>
+        <v>124692.33</v>
       </c>
       <c r="E4" t="n">
-        <v>-121551.9</v>
+        <v>-121190.8</v>
       </c>
       <c r="F4" t="n">
-        <v>522.67</v>
+        <v>525.23</v>
       </c>
       <c r="G4" t="n">
-        <v>5725.78</v>
+        <v>4040.2</v>
       </c>
       <c r="H4" t="n">
-        <v>-66710.21000000001</v>
+        <v>-89670.94</v>
       </c>
       <c r="I4" t="n">
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>395103.99</v>
+        <v>379026.16</v>
       </c>
     </row>
     <row r="5">
@@ -1038,31 +1038,31 @@
         <v>2003</v>
       </c>
       <c r="B5" t="n">
-        <v>607294.77</v>
+        <v>581073.08</v>
       </c>
       <c r="C5" t="n">
-        <v>3636.15</v>
+        <v>2920.82</v>
       </c>
       <c r="D5" t="n">
-        <v>67960.06</v>
+        <v>70567.45</v>
       </c>
       <c r="E5" t="n">
-        <v>-64323.91</v>
+        <v>-67646.63</v>
       </c>
       <c r="F5" t="n">
-        <v>545.42</v>
+        <v>438.12</v>
       </c>
       <c r="G5" t="n">
-        <v>6271.21</v>
+        <v>4478.32</v>
       </c>
       <c r="H5" t="n">
-        <v>-183776.94</v>
+        <v>-193682.92</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>313522.81</v>
+        <v>297202.13</v>
       </c>
     </row>
     <row r="6">
@@ -1070,31 +1070,31 @@
         <v>2004</v>
       </c>
       <c r="B6" t="n">
-        <v>747242.49</v>
+        <v>732002.21</v>
       </c>
       <c r="C6" t="n">
-        <v>31241.4</v>
+        <v>25425.61</v>
       </c>
       <c r="D6" t="n">
-        <v>40774.65</v>
+        <v>38077.62</v>
       </c>
       <c r="E6" t="n">
-        <v>-9533.26</v>
+        <v>-12652.01</v>
       </c>
       <c r="F6" t="n">
-        <v>4686.21</v>
+        <v>3813.84</v>
       </c>
       <c r="G6" t="n">
-        <v>10957.42</v>
+        <v>8292.17</v>
       </c>
       <c r="H6" t="n">
-        <v>-34295.96</v>
+        <v>-30101.78</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>415640.3</v>
+        <v>405547.98</v>
       </c>
     </row>
     <row r="7">
@@ -1102,31 +1102,31 @@
         <v>2005</v>
       </c>
       <c r="B7" t="n">
-        <v>821799.26</v>
+        <v>800729.73</v>
       </c>
       <c r="C7" t="n">
-        <v>48528.85</v>
+        <v>42800.58</v>
       </c>
       <c r="D7" t="n">
-        <v>31201.6</v>
+        <v>28187.39</v>
       </c>
       <c r="E7" t="n">
-        <v>17327.24</v>
+        <v>14613.19</v>
       </c>
       <c r="F7" t="n">
-        <v>7279.33</v>
+        <v>6420.09</v>
       </c>
       <c r="G7" t="n">
-        <v>18236.74</v>
+        <v>14712.25</v>
       </c>
       <c r="H7" t="n">
-        <v>22933.56</v>
+        <v>24012.55</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>446409.38</v>
+        <v>432641.99</v>
       </c>
     </row>
     <row r="8">
@@ -1134,31 +1134,31 @@
         <v>2006</v>
       </c>
       <c r="B8" t="n">
-        <v>837688.46</v>
+        <v>811801.5600000001</v>
       </c>
       <c r="C8" t="n">
-        <v>36010.87</v>
+        <v>35229.96</v>
       </c>
       <c r="D8" t="n">
-        <v>35342.2</v>
+        <v>31557.97</v>
       </c>
       <c r="E8" t="n">
-        <v>668.67</v>
+        <v>3671.98</v>
       </c>
       <c r="F8" t="n">
-        <v>5401.63</v>
+        <v>5284.49</v>
       </c>
       <c r="G8" t="n">
-        <v>23638.37</v>
+        <v>19996.75</v>
       </c>
       <c r="H8" t="n">
-        <v>38154.1</v>
+        <v>31412.4</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>481540.87</v>
+        <v>463147.25</v>
       </c>
     </row>
     <row r="9">
@@ -1166,31 +1166,31 @@
         <v>2007</v>
       </c>
       <c r="B9" t="n">
-        <v>952479.64</v>
+        <v>942493.0600000001</v>
       </c>
       <c r="C9" t="n">
-        <v>36788.24</v>
+        <v>42560.89</v>
       </c>
       <c r="D9" t="n">
-        <v>9460.200000000001</v>
+        <v>8189.07</v>
       </c>
       <c r="E9" t="n">
-        <v>27328.04</v>
+        <v>34371.82</v>
       </c>
       <c r="F9" t="n">
-        <v>5518.24</v>
+        <v>6384.13</v>
       </c>
       <c r="G9" t="n">
-        <v>29156.61</v>
+        <v>26380.88</v>
       </c>
       <c r="H9" t="n">
-        <v>125617.23</v>
+        <v>127732.08</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>516406.76</v>
+        <v>511419.32</v>
       </c>
     </row>
     <row r="10">
@@ -1198,31 +1198,31 @@
         <v>2008</v>
       </c>
       <c r="B10" t="n">
-        <v>1042307.35</v>
+        <v>999097.95</v>
       </c>
       <c r="C10" t="n">
-        <v>82996.98</v>
+        <v>54219</v>
       </c>
       <c r="D10" t="n">
-        <v>17992.89</v>
+        <v>18840.72</v>
       </c>
       <c r="E10" t="n">
-        <v>65004.09</v>
+        <v>35378.28</v>
       </c>
       <c r="F10" t="n">
-        <v>12449.55</v>
+        <v>8132.85</v>
       </c>
       <c r="G10" t="n">
-        <v>41606.16</v>
+        <v>34513.73</v>
       </c>
       <c r="H10" t="n">
-        <v>150440.84</v>
+        <v>148958.69</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>457139.93</v>
+        <v>411915.07</v>
       </c>
     </row>
     <row r="11">
@@ -1230,31 +1230,31 @@
         <v>2009</v>
       </c>
       <c r="B11" t="n">
-        <v>733288.76</v>
+        <v>662056.96</v>
       </c>
       <c r="C11" t="n">
-        <v>54128.13</v>
+        <v>27326.53</v>
       </c>
       <c r="D11" t="n">
-        <v>99360.02</v>
+        <v>96403.92999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-45231.89</v>
+        <v>-69077.39999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>8119.22</v>
+        <v>4098.98</v>
       </c>
       <c r="G11" t="n">
-        <v>49725.38</v>
+        <v>38612.71</v>
       </c>
       <c r="H11" t="n">
-        <v>-113345.86</v>
+        <v>-119004.91</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>471798.78</v>
+        <v>407430.34</v>
       </c>
     </row>
     <row r="12">
@@ -1262,31 +1262,31 @@
         <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>857779.1899999999</v>
+        <v>799283.97</v>
       </c>
       <c r="C12" t="n">
-        <v>49726.35</v>
+        <v>44115.04</v>
       </c>
       <c r="D12" t="n">
-        <v>27735.33</v>
+        <v>27109.25</v>
       </c>
       <c r="E12" t="n">
-        <v>21991.03</v>
+        <v>17005.8</v>
       </c>
       <c r="F12" t="n">
-        <v>7458.95</v>
+        <v>6617.26</v>
       </c>
       <c r="G12" t="n">
-        <v>57184.33</v>
+        <v>45229.97</v>
       </c>
       <c r="H12" t="n">
-        <v>-10846.45</v>
+        <v>1216.31</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>562858.02</v>
+        <v>523048.57</v>
       </c>
     </row>
     <row r="13">
@@ -1294,31 +1294,31 @@
         <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>936682.89</v>
+        <v>886071.75</v>
       </c>
       <c r="C13" t="n">
-        <v>28642.86</v>
+        <v>27756.62</v>
       </c>
       <c r="D13" t="n">
-        <v>39017.56</v>
+        <v>27148.53</v>
       </c>
       <c r="E13" t="n">
-        <v>-10374.7</v>
+        <v>608.09</v>
       </c>
       <c r="F13" t="n">
-        <v>4296.43</v>
+        <v>4163.49</v>
       </c>
       <c r="G13" t="n">
-        <v>61480.76</v>
+        <v>49393.46</v>
       </c>
       <c r="H13" t="n">
-        <v>78431.95</v>
+        <v>87396</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>455930.16</v>
+        <v>431343.8</v>
       </c>
     </row>
     <row r="14">
@@ -1326,31 +1326,31 @@
         <v>2012</v>
       </c>
       <c r="B14" t="n">
-        <v>959971.22</v>
+        <v>916792.83</v>
       </c>
       <c r="C14" t="n">
-        <v>39440.95</v>
+        <v>39070.75</v>
       </c>
       <c r="D14" t="n">
-        <v>7633.5</v>
+        <v>6193.6</v>
       </c>
       <c r="E14" t="n">
-        <v>31807.45</v>
+        <v>32877.15</v>
       </c>
       <c r="F14" t="n">
-        <v>5916.14</v>
+        <v>5860.61</v>
       </c>
       <c r="G14" t="n">
-        <v>67396.89999999999</v>
+        <v>55254.07</v>
       </c>
       <c r="H14" t="n">
-        <v>69912.83</v>
+        <v>85239.92999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>445075.72</v>
+        <v>422787.76</v>
       </c>
     </row>
     <row r="15">
@@ -1358,31 +1358,31 @@
         <v>2013</v>
       </c>
       <c r="B15" t="n">
-        <v>1117895.68</v>
+        <v>1081014.52</v>
       </c>
       <c r="C15" t="n">
-        <v>69252.85000000001</v>
+        <v>78868.35000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>7728.86</v>
+        <v>4166.21</v>
       </c>
       <c r="E15" t="n">
-        <v>61524</v>
+        <v>74702.14</v>
       </c>
       <c r="F15" t="n">
-        <v>10387.93</v>
+        <v>11830.25</v>
       </c>
       <c r="G15" t="n">
-        <v>77784.83</v>
+        <v>67084.32000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>166313.3</v>
+        <v>174759.49</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>556420.4</v>
+        <v>552827.91</v>
       </c>
     </row>
     <row r="16">
@@ -1390,31 +1390,31 @@
         <v>2014</v>
       </c>
       <c r="B16" t="n">
-        <v>1439807.23</v>
+        <v>1395887.29</v>
       </c>
       <c r="C16" t="n">
-        <v>108047.63</v>
+        <v>103740.68</v>
       </c>
       <c r="D16" t="n">
-        <v>12487.55</v>
+        <v>9357.65</v>
       </c>
       <c r="E16" t="n">
-        <v>95560.08</v>
+        <v>94383.03</v>
       </c>
       <c r="F16" t="n">
-        <v>16207.15</v>
+        <v>15561.1</v>
       </c>
       <c r="G16" t="n">
-        <v>93991.97</v>
+        <v>82645.42999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>392664.77</v>
+        <v>395249.22</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>669591.52</v>
+        <v>654646.97</v>
       </c>
     </row>
     <row r="17">
@@ -1422,31 +1422,31 @@
         <v>2015</v>
       </c>
       <c r="B17" t="n">
-        <v>1666503.48</v>
+        <v>1579068.12</v>
       </c>
       <c r="C17" t="n">
-        <v>186545.43</v>
+        <v>161957.39</v>
       </c>
       <c r="D17" t="n">
-        <v>20750.29</v>
+        <v>13646.03</v>
       </c>
       <c r="E17" t="n">
-        <v>165795.14</v>
+        <v>148311.36</v>
       </c>
       <c r="F17" t="n">
-        <v>27981.81</v>
+        <v>24293.61</v>
       </c>
       <c r="G17" t="n">
-        <v>121973.79</v>
+        <v>106939.03</v>
       </c>
       <c r="H17" t="n">
-        <v>453565.88</v>
+        <v>430118.69</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>851584.41</v>
+        <v>790376.4399999999</v>
       </c>
     </row>
     <row r="18">
@@ -1454,31 +1454,31 @@
         <v>2016</v>
       </c>
       <c r="B18" t="n">
-        <v>1765565.94</v>
+        <v>1664880.21</v>
       </c>
       <c r="C18" t="n">
-        <v>120837.08</v>
+        <v>122843.04</v>
       </c>
       <c r="D18" t="n">
-        <v>1675.55</v>
+        <v>1455.36</v>
       </c>
       <c r="E18" t="n">
-        <v>119161.54</v>
+        <v>121387.69</v>
       </c>
       <c r="F18" t="n">
-        <v>18125.56</v>
+        <v>18426.46</v>
       </c>
       <c r="G18" t="n">
-        <v>140099.35</v>
+        <v>125365.49</v>
       </c>
       <c r="H18" t="n">
-        <v>433466.8</v>
+        <v>394543.09</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>928516.2</v>
+        <v>882876.28</v>
       </c>
     </row>
     <row r="19">
@@ -1486,31 +1486,31 @@
         <v>2017</v>
       </c>
       <c r="B19" t="n">
-        <v>1993551.11</v>
+        <v>1845142.66</v>
       </c>
       <c r="C19" t="n">
-        <v>171407.01</v>
+        <v>156857.39</v>
       </c>
       <c r="D19" t="n">
-        <v>7205.03</v>
+        <v>8537.51</v>
       </c>
       <c r="E19" t="n">
-        <v>164201.98</v>
+        <v>148319.89</v>
       </c>
       <c r="F19" t="n">
-        <v>25711.05</v>
+        <v>23528.61</v>
       </c>
       <c r="G19" t="n">
-        <v>165810.4</v>
+        <v>148894.1</v>
       </c>
       <c r="H19" t="n">
-        <v>497249.99</v>
+        <v>426485.66</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>993920.53</v>
+        <v>920213.13</v>
       </c>
     </row>
     <row r="20">
@@ -1518,31 +1518,31 @@
         <v>2018</v>
       </c>
       <c r="B20" t="n">
-        <v>2439383.77</v>
+        <v>2270386.88</v>
       </c>
       <c r="C20" t="n">
-        <v>183184.78</v>
+        <v>167932.02</v>
       </c>
       <c r="D20" t="n">
-        <v>7798.88</v>
+        <v>6462.44</v>
       </c>
       <c r="E20" t="n">
-        <v>175385.9</v>
+        <v>161469.57</v>
       </c>
       <c r="F20" t="n">
-        <v>27477.72</v>
+        <v>25189.8</v>
       </c>
       <c r="G20" t="n">
-        <v>193288.12</v>
+        <v>174083.9</v>
       </c>
       <c r="H20" t="n">
-        <v>767696.76</v>
+        <v>690260.3100000001</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1080441.82</v>
+        <v>998277.37</v>
       </c>
     </row>
     <row r="21">
@@ -1550,31 +1550,31 @@
         <v>2019</v>
       </c>
       <c r="B21" t="n">
-        <v>2377565.51</v>
+        <v>2212895.46</v>
       </c>
       <c r="C21" t="n">
-        <v>224032.29</v>
+        <v>213868.07</v>
       </c>
       <c r="D21" t="n">
-        <v>58311.09</v>
+        <v>54921.39</v>
       </c>
       <c r="E21" t="n">
-        <v>165721.2</v>
+        <v>158946.68</v>
       </c>
       <c r="F21" t="n">
-        <v>33604.84</v>
+        <v>32080.21</v>
       </c>
       <c r="G21" t="n">
-        <v>226892.96</v>
+        <v>206164.11</v>
       </c>
       <c r="H21" t="n">
-        <v>540157.29</v>
+        <v>473822.21</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1500827.5</v>
+        <v>1402935.39</v>
       </c>
     </row>
     <row r="22">
@@ -1582,31 +1582,31 @@
         <v>2020</v>
       </c>
       <c r="B22" t="n">
-        <v>3156109.62</v>
+        <v>2933282.97</v>
       </c>
       <c r="C22" t="n">
-        <v>285583.66</v>
+        <v>250623.79</v>
       </c>
       <c r="D22" t="n">
-        <v>11735.53</v>
+        <v>12335.88</v>
       </c>
       <c r="E22" t="n">
-        <v>273848.13</v>
+        <v>238287.91</v>
       </c>
       <c r="F22" t="n">
-        <v>42837.55</v>
+        <v>37593.57</v>
       </c>
       <c r="G22" t="n">
-        <v>269730.51</v>
+        <v>243757.68</v>
       </c>
       <c r="H22" t="n">
-        <v>1044853.27</v>
+        <v>955921.8</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1304455.66</v>
+        <v>1204130.54</v>
       </c>
     </row>
     <row r="23">
@@ -1614,31 +1614,31 @@
         <v>2021</v>
       </c>
       <c r="B23" t="n">
-        <v>3695504.48</v>
+        <v>3464897.53</v>
       </c>
       <c r="C23" t="n">
-        <v>267327.71</v>
+        <v>250495.27</v>
       </c>
       <c r="D23" t="n">
-        <v>23400.82</v>
+        <v>19157.29</v>
       </c>
       <c r="E23" t="n">
-        <v>243926.89</v>
+        <v>231337.97</v>
       </c>
       <c r="F23" t="n">
-        <v>40099.16</v>
+        <v>37574.29</v>
       </c>
       <c r="G23" t="n">
-        <v>309829.67</v>
+        <v>281331.97</v>
       </c>
       <c r="H23" t="n">
-        <v>1340321.24</v>
+        <v>1256198.39</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1495722.86</v>
+        <v>1392718.29</v>
       </c>
     </row>
     <row r="24">
@@ -1646,31 +1646,31 @@
         <v>2022</v>
       </c>
       <c r="B24" t="n">
-        <v>4773784.57</v>
+        <v>4403806.1</v>
       </c>
       <c r="C24" t="n">
-        <v>475242.18</v>
+        <v>414050.12</v>
       </c>
       <c r="D24" t="n">
-        <v>789.98</v>
+        <v>904.15</v>
       </c>
       <c r="E24" t="n">
-        <v>474452.19</v>
+        <v>413145.96</v>
       </c>
       <c r="F24" t="n">
-        <v>71286.33</v>
+        <v>62107.52</v>
       </c>
       <c r="G24" t="n">
-        <v>381115.99</v>
+        <v>343439.49</v>
       </c>
       <c r="H24" t="n">
-        <v>1944149.13</v>
+        <v>1781961</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2093560.68</v>
+        <v>1912404.49</v>
       </c>
     </row>
     <row r="25">
@@ -1678,31 +1678,31 @@
         <v>2023</v>
       </c>
       <c r="B25" t="n">
-        <v>3890741.06</v>
+        <v>3594273.01</v>
       </c>
       <c r="C25" t="n">
-        <v>336022.47</v>
+        <v>298709.66</v>
       </c>
       <c r="D25" t="n">
-        <v>69665.49000000001</v>
+        <v>61593.38</v>
       </c>
       <c r="E25" t="n">
-        <v>266356.98</v>
+        <v>237116.28</v>
       </c>
       <c r="F25" t="n">
-        <v>50403.37</v>
+        <v>44806.45</v>
       </c>
       <c r="G25" t="n">
-        <v>431519.37</v>
+        <v>388245.94</v>
       </c>
       <c r="H25" t="n">
-        <v>794748.65</v>
+        <v>735311.63</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1997650.02</v>
+        <v>1822657.18</v>
       </c>
     </row>
     <row r="26">
@@ -1710,31 +1710,31 @@
         <v>2024</v>
       </c>
       <c r="B26" t="n">
-        <v>5089211.64</v>
+        <v>4636488.72</v>
       </c>
       <c r="C26" t="n">
-        <v>328349.14</v>
+        <v>284075.35</v>
       </c>
       <c r="D26" t="n">
-        <v>47812.1</v>
+        <v>44915.54</v>
       </c>
       <c r="E26" t="n">
-        <v>280537.04</v>
+        <v>239159.81</v>
       </c>
       <c r="F26" t="n">
-        <v>49252.37</v>
+        <v>42611.3</v>
       </c>
       <c r="G26" t="n">
-        <v>480771.74</v>
+        <v>430857.24</v>
       </c>
       <c r="H26" t="n">
-        <v>1712682.18</v>
+        <v>1538367.53</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2326991.61</v>
+        <v>2067346.16</v>
       </c>
     </row>
     <row r="27">
@@ -1742,31 +1742,31 @@
         <v>2025</v>
       </c>
       <c r="B27" t="n">
-        <v>6497794.47</v>
+        <v>5875583.02</v>
       </c>
       <c r="C27" t="n">
-        <v>477654.25</v>
+        <v>440402.02</v>
       </c>
       <c r="D27" t="n">
-        <v>51608.83</v>
+        <v>48323.9</v>
       </c>
       <c r="E27" t="n">
-        <v>426045.42</v>
+        <v>392078.12</v>
       </c>
       <c r="F27" t="n">
-        <v>71648.14</v>
+        <v>66060.3</v>
       </c>
       <c r="G27" t="n">
-        <v>552419.87</v>
+        <v>496917.54</v>
       </c>
       <c r="H27" t="n">
-        <v>2695219.59</v>
+        <v>2385383.71</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2581257.46</v>
+        <v>2361892.77</v>
       </c>
     </row>
     <row r="28">
@@ -1774,7 +1774,7 @@
         <v>2026</v>
       </c>
       <c r="B28" t="n">
-        <v>7774865.39</v>
+        <v>7021489.32</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -1789,10 +1789,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>552419.87</v>
+        <v>496917.54</v>
       </c>
       <c r="H28" t="n">
-        <v>3972290.51</v>
+        <v>3531290.01</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -1904,16 +1904,16 @@
         <v>2001</v>
       </c>
       <c r="B3" t="n">
-        <v>894745.09</v>
+        <v>873104</v>
       </c>
       <c r="C3" t="n">
-        <v>34687.41</v>
+        <v>23433.16</v>
       </c>
       <c r="D3" t="n">
-        <v>57739.89</v>
+        <v>59839.72</v>
       </c>
       <c r="E3" t="n">
-        <v>-23052.48</v>
+        <v>-36406.57</v>
       </c>
       <c r="F3" t="n">
         <v>0</v>
@@ -1922,13 +1922,13 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>-82202.42999999999</v>
+        <v>-90489.42999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>23052.48</v>
+        <v>36406.57</v>
       </c>
       <c r="J3" t="n">
-        <v>553079.5699999999</v>
+        <v>533680.6800000001</v>
       </c>
     </row>
     <row r="4">
@@ -1936,16 +1936,16 @@
         <v>2002</v>
       </c>
       <c r="B4" t="n">
-        <v>788685.41</v>
+        <v>752731.6899999999</v>
       </c>
       <c r="C4" t="n">
-        <v>3484.49</v>
+        <v>3501.53</v>
       </c>
       <c r="D4" t="n">
-        <v>125036.39</v>
+        <v>124692.33</v>
       </c>
       <c r="E4" t="n">
-        <v>-121551.9</v>
+        <v>-121190.8</v>
       </c>
       <c r="F4" t="n">
         <v>0</v>
@@ -1954,13 +1954,13 @@
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>-66710.21000000001</v>
+        <v>-89670.94</v>
       </c>
       <c r="I4" t="n">
-        <v>144604.38</v>
+        <v>157597.37</v>
       </c>
       <c r="J4" t="n">
-        <v>395103.99</v>
+        <v>379026.16</v>
       </c>
     </row>
     <row r="5">
@@ -1968,16 +1968,16 @@
         <v>2003</v>
       </c>
       <c r="B5" t="n">
-        <v>607294.77</v>
+        <v>581073.08</v>
       </c>
       <c r="C5" t="n">
-        <v>3636.15</v>
+        <v>2920.82</v>
       </c>
       <c r="D5" t="n">
-        <v>67960.06</v>
+        <v>70567.45</v>
       </c>
       <c r="E5" t="n">
-        <v>-64323.91</v>
+        <v>-67646.63</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -1986,13 +1986,13 @@
         <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>-183776.94</v>
+        <v>-193682.92</v>
       </c>
       <c r="I5" t="n">
-        <v>208928.29</v>
+        <v>225244</v>
       </c>
       <c r="J5" t="n">
-        <v>313522.81</v>
+        <v>297202.13</v>
       </c>
     </row>
     <row r="6">
@@ -2000,16 +2000,16 @@
         <v>2004</v>
       </c>
       <c r="B6" t="n">
-        <v>747242.49</v>
+        <v>732002.21</v>
       </c>
       <c r="C6" t="n">
-        <v>31241.4</v>
+        <v>25425.61</v>
       </c>
       <c r="D6" t="n">
-        <v>40774.65</v>
+        <v>38077.62</v>
       </c>
       <c r="E6" t="n">
-        <v>-9533.26</v>
+        <v>-12652.01</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
@@ -2018,13 +2018,13 @@
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-34295.96</v>
+        <v>-30101.78</v>
       </c>
       <c r="I6" t="n">
-        <v>218461.55</v>
+        <v>237896.01</v>
       </c>
       <c r="J6" t="n">
-        <v>415640.3</v>
+        <v>405547.98</v>
       </c>
     </row>
     <row r="7">
@@ -2032,16 +2032,16 @@
         <v>2005</v>
       </c>
       <c r="B7" t="n">
-        <v>821799.26</v>
+        <v>800729.73</v>
       </c>
       <c r="C7" t="n">
-        <v>48528.85</v>
+        <v>42800.58</v>
       </c>
       <c r="D7" t="n">
-        <v>31201.6</v>
+        <v>28187.39</v>
       </c>
       <c r="E7" t="n">
-        <v>17327.24</v>
+        <v>14613.19</v>
       </c>
       <c r="F7" t="n">
         <v>0</v>
@@ -2050,13 +2050,13 @@
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>22933.56</v>
+        <v>24012.55</v>
       </c>
       <c r="I7" t="n">
-        <v>201134.31</v>
+        <v>223282.82</v>
       </c>
       <c r="J7" t="n">
-        <v>446409.38</v>
+        <v>432641.99</v>
       </c>
     </row>
     <row r="8">
@@ -2064,16 +2064,16 @@
         <v>2006</v>
       </c>
       <c r="B8" t="n">
-        <v>837688.46</v>
+        <v>811801.5600000001</v>
       </c>
       <c r="C8" t="n">
-        <v>36010.87</v>
+        <v>35229.96</v>
       </c>
       <c r="D8" t="n">
-        <v>35342.2</v>
+        <v>31557.97</v>
       </c>
       <c r="E8" t="n">
-        <v>668.67</v>
+        <v>3671.98</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
@@ -2082,13 +2082,13 @@
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>38154.1</v>
+        <v>31412.4</v>
       </c>
       <c r="I8" t="n">
-        <v>200465.63</v>
+        <v>219610.83</v>
       </c>
       <c r="J8" t="n">
-        <v>481540.87</v>
+        <v>463147.25</v>
       </c>
     </row>
     <row r="9">
@@ -2096,16 +2096,16 @@
         <v>2007</v>
       </c>
       <c r="B9" t="n">
-        <v>952479.64</v>
+        <v>942493.0600000001</v>
       </c>
       <c r="C9" t="n">
-        <v>36788.24</v>
+        <v>42560.89</v>
       </c>
       <c r="D9" t="n">
-        <v>9460.200000000001</v>
+        <v>8189.07</v>
       </c>
       <c r="E9" t="n">
-        <v>27328.04</v>
+        <v>34371.82</v>
       </c>
       <c r="F9" t="n">
         <v>0</v>
@@ -2114,13 +2114,13 @@
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>125617.23</v>
+        <v>127732.08</v>
       </c>
       <c r="I9" t="n">
-        <v>173137.59</v>
+        <v>185239.01</v>
       </c>
       <c r="J9" t="n">
-        <v>516406.76</v>
+        <v>511419.32</v>
       </c>
     </row>
     <row r="10">
@@ -2128,16 +2128,16 @@
         <v>2008</v>
       </c>
       <c r="B10" t="n">
-        <v>1042307.35</v>
+        <v>999097.95</v>
       </c>
       <c r="C10" t="n">
-        <v>82996.98</v>
+        <v>54219</v>
       </c>
       <c r="D10" t="n">
-        <v>17992.89</v>
+        <v>18840.72</v>
       </c>
       <c r="E10" t="n">
-        <v>65004.09</v>
+        <v>35378.28</v>
       </c>
       <c r="F10" t="n">
         <v>0</v>
@@ -2146,13 +2146,13 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>150440.84</v>
+        <v>148958.69</v>
       </c>
       <c r="I10" t="n">
-        <v>108133.5</v>
+        <v>149860.74</v>
       </c>
       <c r="J10" t="n">
-        <v>457139.93</v>
+        <v>411915.07</v>
       </c>
     </row>
     <row r="11">
@@ -2160,16 +2160,16 @@
         <v>2009</v>
       </c>
       <c r="B11" t="n">
-        <v>733288.76</v>
+        <v>662056.96</v>
       </c>
       <c r="C11" t="n">
-        <v>54128.13</v>
+        <v>27326.53</v>
       </c>
       <c r="D11" t="n">
-        <v>99360.02</v>
+        <v>96403.92999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>-45231.89</v>
+        <v>-69077.39999999999</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
@@ -2178,13 +2178,13 @@
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-113345.86</v>
+        <v>-119004.91</v>
       </c>
       <c r="I11" t="n">
-        <v>153365.39</v>
+        <v>218938.13</v>
       </c>
       <c r="J11" t="n">
-        <v>471798.78</v>
+        <v>407430.34</v>
       </c>
     </row>
     <row r="12">
@@ -2192,16 +2192,16 @@
         <v>2010</v>
       </c>
       <c r="B12" t="n">
-        <v>857779.1899999999</v>
+        <v>799283.97</v>
       </c>
       <c r="C12" t="n">
-        <v>49726.35</v>
+        <v>44115.04</v>
       </c>
       <c r="D12" t="n">
-        <v>27735.33</v>
+        <v>27109.25</v>
       </c>
       <c r="E12" t="n">
-        <v>21991.03</v>
+        <v>17005.8</v>
       </c>
       <c r="F12" t="n">
         <v>0</v>
@@ -2210,13 +2210,13 @@
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-10846.45</v>
+        <v>1216.31</v>
       </c>
       <c r="I12" t="n">
-        <v>131374.36</v>
+        <v>201932.34</v>
       </c>
       <c r="J12" t="n">
-        <v>562858.02</v>
+        <v>523048.57</v>
       </c>
     </row>
     <row r="13">
@@ -2224,16 +2224,16 @@
         <v>2011</v>
       </c>
       <c r="B13" t="n">
-        <v>936682.89</v>
+        <v>886071.75</v>
       </c>
       <c r="C13" t="n">
-        <v>28642.86</v>
+        <v>27756.62</v>
       </c>
       <c r="D13" t="n">
-        <v>39017.56</v>
+        <v>27148.53</v>
       </c>
       <c r="E13" t="n">
-        <v>-10374.7</v>
+        <v>608.09</v>
       </c>
       <c r="F13" t="n">
         <v>0</v>
@@ -2242,13 +2242,13 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>78431.95</v>
+        <v>87396</v>
       </c>
       <c r="I13" t="n">
-        <v>141749.06</v>
+        <v>201324.25</v>
       </c>
       <c r="J13" t="n">
-        <v>455930.16</v>
+        <v>431343.8</v>
       </c>
     </row>
     <row r="14">
@@ -2256,16 +2256,16 @@
         <v>2012</v>
       </c>
       <c r="B14" t="n">
-        <v>959971.22</v>
+        <v>916792.83</v>
       </c>
       <c r="C14" t="n">
-        <v>39440.95</v>
+        <v>39070.75</v>
       </c>
       <c r="D14" t="n">
-        <v>7633.5</v>
+        <v>6193.6</v>
       </c>
       <c r="E14" t="n">
-        <v>31807.45</v>
+        <v>32877.15</v>
       </c>
       <c r="F14" t="n">
         <v>0</v>
@@ -2274,13 +2274,13 @@
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>69912.83</v>
+        <v>85239.92999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>109941.61</v>
+        <v>168447.1</v>
       </c>
       <c r="J14" t="n">
-        <v>445075.72</v>
+        <v>422787.76</v>
       </c>
     </row>
     <row r="15">
@@ -2288,16 +2288,16 @@
         <v>2013</v>
       </c>
       <c r="B15" t="n">
-        <v>1117895.68</v>
+        <v>1081014.52</v>
       </c>
       <c r="C15" t="n">
-        <v>69252.85000000001</v>
+        <v>78868.35000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>7728.86</v>
+        <v>4166.21</v>
       </c>
       <c r="E15" t="n">
-        <v>61524</v>
+        <v>74702.14</v>
       </c>
       <c r="F15" t="n">
         <v>0</v>
@@ -2306,13 +2306,13 @@
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>166313.3</v>
+        <v>174759.49</v>
       </c>
       <c r="I15" t="n">
-        <v>48417.62</v>
+        <v>93744.96000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>556420.4</v>
+        <v>552827.91</v>
       </c>
     </row>
     <row r="16">
@@ -2320,31 +2320,31 @@
         <v>2014</v>
       </c>
       <c r="B16" t="n">
-        <v>1439807.23</v>
+        <v>1395887.29</v>
       </c>
       <c r="C16" t="n">
-        <v>108047.63</v>
+        <v>103740.68</v>
       </c>
       <c r="D16" t="n">
-        <v>12487.55</v>
+        <v>9357.65</v>
       </c>
       <c r="E16" t="n">
-        <v>95560.08</v>
+        <v>94383.03</v>
       </c>
       <c r="F16" t="n">
-        <v>7071.37</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>7071.37</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>392664.77</v>
+        <v>395249.22</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>669591.52</v>
+        <v>654646.97</v>
       </c>
     </row>
     <row r="17">
@@ -2352,31 +2352,31 @@
         <v>2015</v>
       </c>
       <c r="B17" t="n">
-        <v>1666503.48</v>
+        <v>1579068.12</v>
       </c>
       <c r="C17" t="n">
-        <v>186545.43</v>
+        <v>161957.39</v>
       </c>
       <c r="D17" t="n">
-        <v>20750.29</v>
+        <v>13646.03</v>
       </c>
       <c r="E17" t="n">
-        <v>165795.14</v>
+        <v>148311.36</v>
       </c>
       <c r="F17" t="n">
-        <v>24869.27</v>
+        <v>22246.7</v>
       </c>
       <c r="G17" t="n">
-        <v>31940.64</v>
+        <v>22342.41</v>
       </c>
       <c r="H17" t="n">
-        <v>453565.88</v>
+        <v>430118.69</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>851584.41</v>
+        <v>790376.4399999999</v>
       </c>
     </row>
     <row r="18">
@@ -2384,31 +2384,31 @@
         <v>2016</v>
       </c>
       <c r="B18" t="n">
-        <v>1765565.94</v>
+        <v>1664880.21</v>
       </c>
       <c r="C18" t="n">
-        <v>120837.08</v>
+        <v>122843.04</v>
       </c>
       <c r="D18" t="n">
-        <v>1675.55</v>
+        <v>1455.36</v>
       </c>
       <c r="E18" t="n">
-        <v>119161.54</v>
+        <v>121387.69</v>
       </c>
       <c r="F18" t="n">
-        <v>17874.23</v>
+        <v>18208.15</v>
       </c>
       <c r="G18" t="n">
-        <v>49814.87</v>
+        <v>40550.57</v>
       </c>
       <c r="H18" t="n">
-        <v>433466.8</v>
+        <v>394543.09</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
       </c>
       <c r="J18" t="n">
-        <v>928516.2</v>
+        <v>882876.28</v>
       </c>
     </row>
     <row r="19">
@@ -2416,31 +2416,31 @@
         <v>2017</v>
       </c>
       <c r="B19" t="n">
-        <v>1993551.11</v>
+        <v>1845142.66</v>
       </c>
       <c r="C19" t="n">
-        <v>171407.01</v>
+        <v>156857.39</v>
       </c>
       <c r="D19" t="n">
-        <v>7205.03</v>
+        <v>8537.51</v>
       </c>
       <c r="E19" t="n">
-        <v>164201.98</v>
+        <v>148319.89</v>
       </c>
       <c r="F19" t="n">
-        <v>24630.3</v>
+        <v>22247.98</v>
       </c>
       <c r="G19" t="n">
-        <v>74445.17</v>
+        <v>62798.55</v>
       </c>
       <c r="H19" t="n">
-        <v>497249.99</v>
+        <v>426485.66</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>993920.53</v>
+        <v>920213.13</v>
       </c>
     </row>
     <row r="20">
@@ -2448,31 +2448,31 @@
         <v>2018</v>
       </c>
       <c r="B20" t="n">
-        <v>2439383.77</v>
+        <v>2270386.88</v>
       </c>
       <c r="C20" t="n">
-        <v>183184.78</v>
+        <v>167932.02</v>
       </c>
       <c r="D20" t="n">
-        <v>7798.88</v>
+        <v>6462.44</v>
       </c>
       <c r="E20" t="n">
-        <v>175385.9</v>
+        <v>161469.57</v>
       </c>
       <c r="F20" t="n">
-        <v>26307.88</v>
+        <v>24220.44</v>
       </c>
       <c r="G20" t="n">
-        <v>100753.05</v>
+        <v>87018.99000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>767696.76</v>
+        <v>690260.3100000001</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1080441.82</v>
+        <v>998277.37</v>
       </c>
     </row>
     <row r="21">
@@ -2480,31 +2480,31 @@
         <v>2019</v>
       </c>
       <c r="B21" t="n">
-        <v>2377565.51</v>
+        <v>2212895.46</v>
       </c>
       <c r="C21" t="n">
-        <v>224032.29</v>
+        <v>213868.07</v>
       </c>
       <c r="D21" t="n">
-        <v>58311.09</v>
+        <v>54921.39</v>
       </c>
       <c r="E21" t="n">
-        <v>165721.2</v>
+        <v>158946.68</v>
       </c>
       <c r="F21" t="n">
-        <v>24858.18</v>
+        <v>23842</v>
       </c>
       <c r="G21" t="n">
-        <v>125611.23</v>
+        <v>110860.99</v>
       </c>
       <c r="H21" t="n">
-        <v>540157.29</v>
+        <v>473822.21</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>1500827.5</v>
+        <v>1402935.39</v>
       </c>
     </row>
     <row r="22">
@@ -2512,31 +2512,31 @@
         <v>2020</v>
       </c>
       <c r="B22" t="n">
-        <v>3156109.62</v>
+        <v>2933282.97</v>
       </c>
       <c r="C22" t="n">
-        <v>285583.66</v>
+        <v>250623.79</v>
       </c>
       <c r="D22" t="n">
-        <v>11735.53</v>
+        <v>12335.88</v>
       </c>
       <c r="E22" t="n">
-        <v>273848.13</v>
+        <v>238287.91</v>
       </c>
       <c r="F22" t="n">
-        <v>41077.22</v>
+        <v>35743.19</v>
       </c>
       <c r="G22" t="n">
-        <v>166688.45</v>
+        <v>146604.17</v>
       </c>
       <c r="H22" t="n">
-        <v>1044853.27</v>
+        <v>955921.8</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>1304455.66</v>
+        <v>1204130.54</v>
       </c>
     </row>
     <row r="23">
@@ -2544,31 +2544,31 @@
         <v>2021</v>
       </c>
       <c r="B23" t="n">
-        <v>3695504.48</v>
+        <v>3464897.53</v>
       </c>
       <c r="C23" t="n">
-        <v>267327.71</v>
+        <v>250495.27</v>
       </c>
       <c r="D23" t="n">
-        <v>23400.82</v>
+        <v>19157.29</v>
       </c>
       <c r="E23" t="n">
-        <v>243926.89</v>
+        <v>231337.97</v>
       </c>
       <c r="F23" t="n">
-        <v>36589.03</v>
+        <v>34700.7</v>
       </c>
       <c r="G23" t="n">
-        <v>203277.49</v>
+        <v>181304.87</v>
       </c>
       <c r="H23" t="n">
-        <v>1340321.24</v>
+        <v>1256198.39</v>
       </c>
       <c r="I23" t="n">
         <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>1495722.86</v>
+        <v>1392718.29</v>
       </c>
     </row>
     <row r="24">
@@ -2576,31 +2576,31 @@
         <v>2022</v>
       </c>
       <c r="B24" t="n">
-        <v>4773784.57</v>
+        <v>4403806.1</v>
       </c>
       <c r="C24" t="n">
-        <v>475242.18</v>
+        <v>414050.12</v>
       </c>
       <c r="D24" t="n">
-        <v>789.98</v>
+        <v>904.15</v>
       </c>
       <c r="E24" t="n">
-        <v>474452.19</v>
+        <v>413145.96</v>
       </c>
       <c r="F24" t="n">
-        <v>71167.83</v>
+        <v>61971.89</v>
       </c>
       <c r="G24" t="n">
-        <v>274445.32</v>
+        <v>243276.77</v>
       </c>
       <c r="H24" t="n">
-        <v>1944149.13</v>
+        <v>1781961</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
       </c>
       <c r="J24" t="n">
-        <v>2093560.68</v>
+        <v>1912404.49</v>
       </c>
     </row>
     <row r="25">
@@ -2608,31 +2608,31 @@
         <v>2023</v>
       </c>
       <c r="B25" t="n">
-        <v>3890741.06</v>
+        <v>3594273.01</v>
       </c>
       <c r="C25" t="n">
-        <v>336022.47</v>
+        <v>298709.66</v>
       </c>
       <c r="D25" t="n">
-        <v>69665.49000000001</v>
+        <v>61593.38</v>
       </c>
       <c r="E25" t="n">
-        <v>266356.98</v>
+        <v>237116.28</v>
       </c>
       <c r="F25" t="n">
-        <v>39953.55</v>
+        <v>35567.44</v>
       </c>
       <c r="G25" t="n">
-        <v>314398.86</v>
+        <v>278844.21</v>
       </c>
       <c r="H25" t="n">
-        <v>794748.65</v>
+        <v>735311.63</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
       </c>
       <c r="J25" t="n">
-        <v>1997650.02</v>
+        <v>1822657.18</v>
       </c>
     </row>
     <row r="26">
@@ -2640,31 +2640,31 @@
         <v>2024</v>
       </c>
       <c r="B26" t="n">
-        <v>5089211.64</v>
+        <v>4636488.72</v>
       </c>
       <c r="C26" t="n">
-        <v>328349.14</v>
+        <v>284075.35</v>
       </c>
       <c r="D26" t="n">
-        <v>47812.1</v>
+        <v>44915.54</v>
       </c>
       <c r="E26" t="n">
-        <v>280537.04</v>
+        <v>239159.81</v>
       </c>
       <c r="F26" t="n">
-        <v>42080.56</v>
+        <v>35873.97</v>
       </c>
       <c r="G26" t="n">
-        <v>356479.42</v>
+        <v>314718.18</v>
       </c>
       <c r="H26" t="n">
-        <v>1712682.18</v>
+        <v>1538367.53</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>2326991.61</v>
+        <v>2067346.16</v>
       </c>
     </row>
     <row r="27">
@@ -2672,31 +2672,31 @@
         <v>2025</v>
       </c>
       <c r="B27" t="n">
-        <v>6497794.47</v>
+        <v>5875583.02</v>
       </c>
       <c r="C27" t="n">
-        <v>477654.25</v>
+        <v>440402.02</v>
       </c>
       <c r="D27" t="n">
-        <v>51608.83</v>
+        <v>48323.9</v>
       </c>
       <c r="E27" t="n">
-        <v>426045.42</v>
+        <v>392078.12</v>
       </c>
       <c r="F27" t="n">
-        <v>63906.81</v>
+        <v>58811.72</v>
       </c>
       <c r="G27" t="n">
-        <v>420386.23</v>
+        <v>373529.9</v>
       </c>
       <c r="H27" t="n">
-        <v>2695219.59</v>
+        <v>2385383.71</v>
       </c>
       <c r="I27" t="n">
         <v>0</v>
       </c>
       <c r="J27" t="n">
-        <v>2581257.46</v>
+        <v>2361892.77</v>
       </c>
     </row>
     <row r="28">
@@ -2704,7 +2704,7 @@
         <v>2026</v>
       </c>
       <c r="B28" t="n">
-        <v>7774865.39</v>
+        <v>7021489.32</v>
       </c>
       <c r="C28" t="n">
         <v>0</v>
@@ -2719,10 +2719,10 @@
         <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>420386.23</v>
+        <v>373529.9</v>
       </c>
       <c r="H28" t="n">
-        <v>3972290.51</v>
+        <v>3531290.01</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -2777,7 +2777,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>$7,774,865</t>
+          <t>$7,021,489</t>
         </is>
       </c>
     </row>
@@ -2789,7 +2789,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>677.5%</t>
+          <t>602.1%</t>
         </is>
       </c>
     </row>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>$3,682,799</t>
+          <t>$3,312,784</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>$880,224</t>
+          <t>$822,584</t>
         </is>
       </c>
     </row>
@@ -2825,7 +2825,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>$552,420</t>
+          <t>$496,918</t>
         </is>
       </c>
     </row>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>$420,386</t>
+          <t>$373,530</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>$132,034</t>
+          <t>$123,388</t>
         </is>
       </c>
     </row>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>25.3%</t>
         </is>
       </c>
     </row>
